--- a/projects/20260324-coop-integration/qa-test-cases-v5.xlsx
+++ b/projects/20260324-coop-integration/qa-test-cases-v5.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Android" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Admin·Server" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="요약" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="테스트 데이터" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,8 +74,14 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -121,8 +128,18 @@
         <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -144,11 +161,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -208,6 +269,24 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -606,13 +685,13 @@
           <t>§1.1 쿠폰 입력</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="30" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -857,13 +936,13 @@
           <t>§1.2 미로그인 처리 (S6 배너)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="30" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1179,13 +1258,13 @@
           <t>§1.3 하트 충전 완료 (S3)</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="30" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1311,13 +1390,13 @@
           <t>§1.4 스킬 이용권 카드 (S4)</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="30" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1603,13 +1682,13 @@
           <t>§1.5 에러 토스트 (S5)</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="30" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1968,13 +2047,13 @@
           <t>§1.6 UI/디자인</t>
         </is>
       </c>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
+      <c r="B47" s="29" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="29" t="n"/>
+      <c r="E47" s="29" t="n"/>
+      <c r="F47" s="29" t="n"/>
+      <c r="G47" s="29" t="n"/>
+      <c r="H47" s="30" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2332,13 +2411,13 @@
           <t>§1.7 다국어</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
+      <c r="B58" s="29" t="n"/>
+      <c r="C58" s="29" t="n"/>
+      <c r="D58" s="29" t="n"/>
+      <c r="E58" s="29" t="n"/>
+      <c r="F58" s="29" t="n"/>
+      <c r="G58" s="29" t="n"/>
+      <c r="H58" s="30" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2541,13 +2620,13 @@
           <t>§1.8 웹뷰 환경</t>
         </is>
       </c>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
+      <c r="B65" s="29" t="n"/>
+      <c r="C65" s="29" t="n"/>
+      <c r="D65" s="29" t="n"/>
+      <c r="E65" s="29" t="n"/>
+      <c r="F65" s="29" t="n"/>
+      <c r="G65" s="29" t="n"/>
+      <c r="H65" s="30" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -2712,13 +2791,13 @@
           <t>§1.9 서버↔웹 크로스 (E2E)</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
+      <c r="B71" s="29" t="n"/>
+      <c r="C71" s="29" t="n"/>
+      <c r="D71" s="29" t="n"/>
+      <c r="E71" s="29" t="n"/>
+      <c r="F71" s="29" t="n"/>
+      <c r="G71" s="29" t="n"/>
+      <c r="H71" s="30" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -3016,13 +3095,13 @@
           <t>§2.1 하트 충전 완료</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="30" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -3110,13 +3189,13 @@
           <t>§2.2 스킬 이용권</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="30" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -3246,13 +3325,13 @@
           <t>§2.3 에러 처리</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="30" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3378,13 +3457,13 @@
           <t>§2.4 중복 탭 방지</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="30" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -3472,13 +3551,13 @@
           <t>§2.5 쿠폰 입력</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="30" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3567,13 +3646,13 @@
           <t>§2.6 팝업 UI/디자인</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="30" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3699,13 +3778,13 @@
           <t>§2.7 다국어</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="29" t="n"/>
+      <c r="H31" s="30" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3869,13 +3948,13 @@
           <t>§2.8 서버↔iOS 크로스</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="29" t="n"/>
+      <c r="H37" s="30" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4045,13 +4124,13 @@
           <t>§2.9 미로그인 처리 (S6)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="30" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4380,13 +4459,13 @@
           <t>§3.1 하트 충전 완료</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="30" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -4474,13 +4553,13 @@
           <t>§3.2 스킬 이용권</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
+      <c r="B8" s="29" t="n"/>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="30" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4648,13 +4727,13 @@
           <t>§3.3 에러 처리</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="30" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4780,13 +4859,13 @@
           <t>§3.4 중복 탭 방지</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4874,13 +4953,13 @@
           <t>§3.5 쿠폰 입력</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="30" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -4969,13 +5048,13 @@
           <t>§3.6 팝업 UI/디자인</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="30" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -5063,13 +5142,13 @@
           <t>§3.7 다국어</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="29" t="n"/>
+      <c r="H31" s="30" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -5233,13 +5312,13 @@
           <t>§3.8 서버↔Android 크로스</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="29" t="n"/>
+      <c r="H37" s="30" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -5405,13 +5484,13 @@
           <t>§3.9 미로그인 처리 (S6)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="30" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -5740,13 +5819,13 @@
           <t>§4.1 POST /api/coupon/register (Phase 1 신규 — P1-R*)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="30" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -6023,13 +6102,13 @@
           <t>§4.2 /api/coupon 프리픽스 가드 (Phase 1 신규 — P1-G*)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="30" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -6210,13 +6289,13 @@
           <t>§4.3 CO_APP_UPDATE_REQUIRED + 구버전 회귀 (P1-E*, P1-C*)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="30" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -6491,13 +6570,13 @@
           <t>§4.4 Admin CouponPrefixRule CRUD (P1-A*)</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="30" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -6725,13 +6804,13 @@
           <t>§4.5 Admin 상품 관리</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="29" t="n"/>
+      <c r="H33" s="30" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -7053,13 +7132,13 @@
           <t>§4.6 Admin 수동 취소 (ISS-001)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="30" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -7303,13 +7382,13 @@
           <t>§4.7 사용 이력 조회</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="29" t="n"/>
+      <c r="H51" s="30" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -7437,13 +7516,13 @@
           <t>§4.8 보안</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
+      <c r="B56" s="29" t="n"/>
+      <c r="C56" s="29" t="n"/>
+      <c r="D56" s="29" t="n"/>
+      <c r="E56" s="29" t="n"/>
+      <c r="F56" s="29" t="n"/>
+      <c r="G56" s="29" t="n"/>
+      <c r="H56" s="30" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -7645,13 +7724,13 @@
           <t>§4.9 성능</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="29" t="n"/>
+      <c r="D63" s="29" t="n"/>
+      <c r="E63" s="29" t="n"/>
+      <c r="F63" s="29" t="n"/>
+      <c r="G63" s="29" t="n"/>
+      <c r="H63" s="30" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -7778,13 +7857,13 @@
           <t>§4.10 Deprecated — Phase 2 제거 예정 (/api/coop/*)</t>
         </is>
       </c>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
+      <c r="B68" s="29" t="n"/>
+      <c r="C68" s="29" t="n"/>
+      <c r="D68" s="29" t="n"/>
+      <c r="E68" s="29" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="29" t="n"/>
+      <c r="H68" s="30" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -8462,9 +8541,9 @@
   <mergeCells count="12">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A43:H43"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A51:H51"/>
@@ -8855,4 +8934,667 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>쿠프마케팅 제공 테스트 쿠폰 (총 16건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>출처: references/Q&amp;A/20260408-dev-env.md (2026-04-20 갱신, 스킬 교환권 6건 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>테스트 환경</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>개발 서버 URL</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>http://test.authapi.inumber.co.kr:9999</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>운영 서버 URL</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>http://authapi.inumber.co.kr:443</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Auth Key (개발=운영 동일)</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>g9PJGmeh6BaSfprJx1xkAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>브랜드코드</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A911</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>프리픽스</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>90 = 카카오 선물하기, 91 = 카카오 외 채널</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>쿠폰 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>쿠폰번호</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>프리픽스</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>상품/스킬명</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>용도/비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>하트 충전권 (10건)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>901914216415</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>유형 명시 없음 — 하트 충전권 기본으로 추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>903276431800</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>906891777783</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>908114272214</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>908590067550</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>910189179684</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>912295658631</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>914053969988</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>914541033704</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>914932940805</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>하트 충전권</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>스킬 교환권 — 정상 (2건)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>906654793410</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>스킬 교환권</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>그 사람과 나의 사주 궁합</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>정상 케이스 (P1-R03 / TC-W-S03 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>911473509612</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>스킬 교환권</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>내 사주에 연애 상대 몇 명 있을까?</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>정상 케이스</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>스킬 교환권 — 결제 취소 (CM_010 검증, 2건)</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>902789585951</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>결제 취소</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>그 사람과 나의 사주 궁합</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>TC-W-E06a / TC-E17 (쿠프마케팅 8099 → CM_010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>916611039014</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>결제 취소</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>내 사주에 연애 상대 몇 명 있을까?</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>스킬 교환권 — 기간 만료 (CM_002 검증, 2건)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>908784177679</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>기간 만료</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>그 사람과 나의 사주 궁합</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>TC-W-E02 (쿠프마케팅 8003 → CM_002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>913767296083</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D32" s="35" t="inlineStr">
+        <is>
+          <t>기간 만료</t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="inlineStr">
+        <is>
+          <t>내 사주에 연애 상대 몇 명 있을까?</t>
+        </is>
+      </c>
+      <c r="F32" s="35" t="inlineStr">
+        <is>
+          <t>동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
+        <is>
+          <t>※ TC-W-E01 (CM_001 유효하지 않은 쿠폰) 검증용 쿠폰은 미제공 — 임의 번호 입력하여 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>※ 사용된 쿠폰은 Admin에서 L2 취소 후 재사용 가능 (쿠프마케팅 측 원복 대기 필요)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>